--- a/i_test/test_D3_coorte_con_bears/med_antipsico.xlsx
+++ b/i_test/test_D3_coorte_con_bears/med_antipsico.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -29,9 +29,6 @@
   </si>
   <si>
     <t xml:space="preserve">Table_cdm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ord</t>
   </si>
   <si>
     <t xml:space="preserve">aic</t>
@@ -145,9 +142,12 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -160,9 +160,7 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="E1" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
